--- a/Can Register Map.xlsx
+++ b/Can Register Map.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\szymo\Downloads\Hiroshima-Motor-Driver-G431-main\Hiroshima-Motor-Driver-G431-main\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tech\robotyka\robots\evangelion-turbo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8F679E1-E578-48B8-B277-40302D05AD0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A68C416D-A56A-41F9-BAE3-A087CA7890E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="2730" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="162">
   <si>
     <t>CAN Instructions</t>
   </si>
@@ -220,9 +220,6 @@
     <t>0x14</t>
   </si>
   <si>
-    <t>Motor A Accel</t>
-  </si>
-  <si>
     <t>Motor B Accel</t>
   </si>
   <si>
@@ -356,9 +353,6 @@
     <t>Motor A Duty</t>
   </si>
   <si>
-    <t>Motor B Duty</t>
-  </si>
-  <si>
     <t>Motor Status</t>
   </si>
   <si>
@@ -606,6 +600,12 @@
   </si>
   <si>
     <t>Error</t>
+  </si>
+  <si>
+    <t>0-200</t>
+  </si>
+  <si>
+    <t>nie dziala lul</t>
   </si>
 </sst>
 </file>
@@ -793,188 +793,188 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1288,73 +1288,73 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="78"/>
-      <c r="B1" s="78"/>
-      <c r="C1" s="80" t="s">
+      <c r="A1" s="34"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="80" t="s">
+      <c r="D1" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="80" t="s">
+      <c r="E1" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="F1" s="80" t="s">
+      <c r="F1" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="G1" s="80" t="s">
+      <c r="G1" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="H1" s="80" t="s">
+      <c r="H1" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="I1" s="80" t="s">
+      <c r="I1" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="J1" s="80" t="s">
+      <c r="J1" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="K1" s="80"/>
-      <c r="L1" s="79"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="76" t="s">
-        <v>95</v>
-      </c>
-      <c r="B2" s="76"/>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
-      <c r="K2" s="76"/>
-      <c r="L2" s="77"/>
+      <c r="A2" s="55" t="s">
+        <v>93</v>
+      </c>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="56"/>
     </row>
     <row r="3" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="54"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="54"/>
-      <c r="D3" s="54"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="54"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="54"/>
-      <c r="I3" s="54"/>
-      <c r="J3" s="54"/>
-      <c r="K3" s="54"/>
-      <c r="L3" s="55"/>
+      <c r="A3" s="57"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="57"/>
+      <c r="L3" s="58"/>
       <c r="O3" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="37" t="s">
+      <c r="A4" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="38"/>
+      <c r="B4" s="50"/>
       <c r="C4" s="11" t="s">
         <v>17</v>
       </c>
@@ -1383,10 +1383,10 @@
       <c r="L4" s="12"/>
     </row>
     <row r="5" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="39"/>
-      <c r="B5" s="40"/>
-      <c r="C5" s="63" t="s">
-        <v>143</v>
+      <c r="A5" s="51"/>
+      <c r="B5" s="52"/>
+      <c r="C5" s="21" t="s">
+        <v>141</v>
       </c>
       <c r="D5" s="13" t="s">
         <v>25</v>
@@ -1413,12 +1413,12 @@
       <c r="L5" s="14"/>
     </row>
     <row r="6" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="37" t="s">
+      <c r="A6" s="49" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="38"/>
-      <c r="C6" s="62" t="s">
-        <v>143</v>
+      <c r="B6" s="50"/>
+      <c r="C6" s="20" t="s">
+        <v>141</v>
       </c>
       <c r="D6" s="11" t="s">
         <v>28</v>
@@ -1447,14 +1447,14 @@
       <c r="L6" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="O6" s="43"/>
-      <c r="P6" s="43"/>
+      <c r="O6" s="79"/>
+      <c r="P6" s="79"/>
       <c r="Q6" s="10"/>
     </row>
     <row r="7" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="39"/>
-      <c r="B7" s="40"/>
-      <c r="C7" s="63"/>
+      <c r="A7" s="51"/>
+      <c r="B7" s="52"/>
+      <c r="C7" s="21"/>
       <c r="D7" s="13"/>
       <c r="E7" s="13" t="s">
         <v>30</v>
@@ -1482,45 +1482,45 @@
       </c>
     </row>
     <row r="8" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="27" t="s">
-        <v>49</v>
-      </c>
-      <c r="B8" s="28"/>
-      <c r="C8" s="64" t="s">
-        <v>143</v>
+      <c r="A8" s="41" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="42"/>
+      <c r="C8" s="22" t="s">
+        <v>141</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>34</v>
       </c>
       <c r="E8" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="G8" s="11" t="s">
         <v>52</v>
-      </c>
-      <c r="G8" s="11" t="s">
-        <v>53</v>
       </c>
       <c r="H8" s="11"/>
       <c r="I8" s="11"/>
       <c r="J8" s="11"/>
       <c r="K8" s="11"/>
       <c r="L8" s="12"/>
-      <c r="O8" s="43" t="s">
+      <c r="O8" s="79" t="s">
         <v>1</v>
       </c>
-      <c r="P8" s="43"/>
+      <c r="P8" s="79"/>
       <c r="Q8" s="10"/>
     </row>
     <row r="9" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
-      <c r="B9" s="32"/>
-      <c r="C9" s="65"/>
+      <c r="A9" s="53"/>
+      <c r="B9" s="54"/>
+      <c r="C9" s="23"/>
       <c r="D9" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F9" s="15" t="s">
         <v>31</v>
@@ -1556,11 +1556,11 @@
       </c>
     </row>
     <row r="10" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="31"/>
-      <c r="B10" s="32"/>
-      <c r="C10" s="65"/>
+      <c r="A10" s="53"/>
+      <c r="B10" s="54"/>
+      <c r="C10" s="23"/>
       <c r="D10" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E10" s="15" t="s">
         <v>29</v>
@@ -1599,11 +1599,11 @@
       </c>
     </row>
     <row r="11" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="29"/>
-      <c r="B11" s="30"/>
-      <c r="C11" s="66"/>
+      <c r="A11" s="43"/>
+      <c r="B11" s="44"/>
+      <c r="C11" s="24"/>
       <c r="D11" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E11" s="13" t="s">
         <v>30</v>
@@ -1638,22 +1638,22 @@
         <v>14</v>
       </c>
       <c r="W11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="21" t="s">
+      <c r="A12" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="22"/>
-      <c r="C12" s="67" t="s">
-        <v>143</v>
+      <c r="B12" s="38"/>
+      <c r="C12" s="25" t="s">
+        <v>141</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>39</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="1" t="s">
@@ -1674,9 +1674,9 @@
       <c r="L12" s="2"/>
     </row>
     <row r="13" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="25"/>
-      <c r="B13" s="26"/>
-      <c r="C13" s="68"/>
+      <c r="A13" s="39"/>
+      <c r="B13" s="40"/>
+      <c r="C13" s="26"/>
       <c r="D13" s="6"/>
       <c r="E13" s="6" t="s">
         <v>36</v>
@@ -1687,25 +1687,25 @@
       <c r="I13" s="6"/>
       <c r="J13" s="6"/>
       <c r="K13" s="6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="L13" s="7" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="33" t="s">
+      <c r="A14" s="45" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="34"/>
-      <c r="C14" s="69" t="s">
-        <v>143</v>
+      <c r="B14" s="46"/>
+      <c r="C14" s="27" t="s">
+        <v>141</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>42</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
@@ -1716,9 +1716,9 @@
       <c r="L14" s="2"/>
     </row>
     <row r="15" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="35"/>
-      <c r="B15" s="36"/>
-      <c r="C15" s="70"/>
+      <c r="A15" s="47"/>
+      <c r="B15" s="48"/>
+      <c r="C15" s="28"/>
       <c r="D15" s="6"/>
       <c r="E15" s="6" t="s">
         <v>40</v>
@@ -1729,23 +1729,23 @@
       <c r="I15" s="6"/>
       <c r="J15" s="6"/>
       <c r="K15" s="6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="L15" s="7"/>
     </row>
     <row r="16" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="21" t="s">
+      <c r="A16" s="37" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="22"/>
-      <c r="C16" s="71" t="s">
-        <v>143</v>
+      <c r="B16" s="38"/>
+      <c r="C16" s="29" t="s">
+        <v>141</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
@@ -1756,9 +1756,9 @@
       <c r="L16" s="2"/>
     </row>
     <row r="17" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="25"/>
-      <c r="B17" s="26"/>
-      <c r="C17" s="72"/>
+      <c r="A17" s="39"/>
+      <c r="B17" s="40"/>
+      <c r="C17" s="30"/>
       <c r="D17" s="6"/>
       <c r="E17" s="6" t="s">
         <v>40</v>
@@ -1769,61 +1769,61 @@
       <c r="I17" s="6"/>
       <c r="J17" s="6"/>
       <c r="K17" s="6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="L17" s="7"/>
     </row>
     <row r="18" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="21" t="s">
+      <c r="A18" s="37" t="s">
+        <v>137</v>
+      </c>
+      <c r="B18" s="38"/>
+      <c r="C18" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="D18" t="s">
+        <v>134</v>
+      </c>
+      <c r="E18" t="s">
+        <v>143</v>
+      </c>
+      <c r="K18" t="s">
+        <v>53</v>
+      </c>
+      <c r="L18" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="B18" s="22"/>
-      <c r="C18" s="73" t="s">
-        <v>143</v>
-      </c>
-      <c r="D18" t="s">
-        <v>136</v>
-      </c>
-      <c r="E18" t="s">
-        <v>145</v>
-      </c>
-      <c r="K18" t="s">
-        <v>54</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>141</v>
-      </c>
     </row>
     <row r="19" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="25"/>
-      <c r="B19" s="26"/>
-      <c r="C19" s="73"/>
+      <c r="A19" s="39"/>
+      <c r="B19" s="40"/>
+      <c r="C19" s="31"/>
       <c r="E19" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="K19" t="s">
         <v>29</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="37" t="s">
+      <c r="A20" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="38"/>
-      <c r="C20" s="62" t="s">
-        <v>143</v>
+      <c r="B20" s="50"/>
+      <c r="C20" s="20" t="s">
+        <v>141</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G20" s="11"/>
       <c r="H20" s="11"/>
@@ -1831,44 +1831,44 @@
       <c r="J20" s="11"/>
       <c r="K20" s="11"/>
       <c r="L20" s="12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="39"/>
-      <c r="B21" s="40"/>
-      <c r="C21" s="63"/>
+      <c r="A21" s="51"/>
+      <c r="B21" s="52"/>
+      <c r="C21" s="21"/>
       <c r="D21" s="13"/>
       <c r="E21" s="13" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G21" s="13"/>
       <c r="H21" s="13"/>
       <c r="I21" s="13"/>
       <c r="J21" s="13"/>
       <c r="K21" s="13" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="L21" s="14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="37" t="s">
-        <v>59</v>
-      </c>
-      <c r="B22" s="38"/>
-      <c r="C22" s="62" t="s">
-        <v>143</v>
+      <c r="A22" s="49" t="s">
+        <v>58</v>
+      </c>
+      <c r="B22" s="50"/>
+      <c r="C22" s="20" t="s">
+        <v>141</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F22" s="11"/>
       <c r="G22" s="11"/>
@@ -1879,9 +1879,9 @@
       <c r="L22" s="12"/>
     </row>
     <row r="23" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="39"/>
-      <c r="B23" s="40"/>
-      <c r="C23" s="63"/>
+      <c r="A23" s="51"/>
+      <c r="B23" s="52"/>
+      <c r="C23" s="21"/>
       <c r="D23" s="13"/>
       <c r="E23" s="13"/>
       <c r="F23" s="13"/>
@@ -1893,18 +1893,18 @@
       <c r="L23" s="14"/>
     </row>
     <row r="24" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="37" t="s">
-        <v>60</v>
-      </c>
-      <c r="B24" s="38"/>
-      <c r="C24" s="62" t="s">
-        <v>143</v>
+      <c r="A24" s="49" t="s">
+        <v>59</v>
+      </c>
+      <c r="B24" s="50"/>
+      <c r="C24" s="20" t="s">
+        <v>141</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F24" s="11"/>
       <c r="G24" s="11"/>
@@ -1915,9 +1915,9 @@
       <c r="L24" s="12"/>
     </row>
     <row r="25" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="39"/>
-      <c r="B25" s="40"/>
-      <c r="C25" s="63"/>
+      <c r="A25" s="51"/>
+      <c r="B25" s="52"/>
+      <c r="C25" s="21"/>
       <c r="D25" s="13"/>
       <c r="E25" s="13"/>
       <c r="F25" s="13"/>
@@ -1929,54 +1929,54 @@
       <c r="L25" s="14"/>
     </row>
     <row r="26" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="50" t="s">
-        <v>94</v>
-      </c>
-      <c r="B26" s="51"/>
-      <c r="C26" s="51"/>
-      <c r="D26" s="51"/>
-      <c r="E26" s="51"/>
-      <c r="F26" s="51"/>
-      <c r="G26" s="51"/>
-      <c r="H26" s="51"/>
-      <c r="I26" s="51"/>
-      <c r="J26" s="51"/>
-      <c r="K26" s="51"/>
-      <c r="L26" s="52"/>
+      <c r="A26" s="59" t="s">
+        <v>92</v>
+      </c>
+      <c r="B26" s="60"/>
+      <c r="C26" s="60"/>
+      <c r="D26" s="60"/>
+      <c r="E26" s="60"/>
+      <c r="F26" s="60"/>
+      <c r="G26" s="60"/>
+      <c r="H26" s="60"/>
+      <c r="I26" s="60"/>
+      <c r="J26" s="60"/>
+      <c r="K26" s="60"/>
+      <c r="L26" s="61"/>
     </row>
     <row r="27" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="53"/>
-      <c r="B27" s="54"/>
-      <c r="C27" s="54"/>
-      <c r="D27" s="54"/>
-      <c r="E27" s="54"/>
-      <c r="F27" s="54"/>
-      <c r="G27" s="54"/>
-      <c r="H27" s="54"/>
-      <c r="I27" s="54"/>
-      <c r="J27" s="54"/>
-      <c r="K27" s="54"/>
-      <c r="L27" s="55"/>
+      <c r="A27" s="62"/>
+      <c r="B27" s="57"/>
+      <c r="C27" s="57"/>
+      <c r="D27" s="57"/>
+      <c r="E27" s="57"/>
+      <c r="F27" s="57"/>
+      <c r="G27" s="57"/>
+      <c r="H27" s="57"/>
+      <c r="I27" s="57"/>
+      <c r="J27" s="57"/>
+      <c r="K27" s="57"/>
+      <c r="L27" s="58"/>
     </row>
     <row r="28" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="B28" s="28"/>
-      <c r="C28" s="64" t="s">
-        <v>143</v>
+      <c r="A28" s="41" t="s">
+        <v>60</v>
+      </c>
+      <c r="B28" s="42"/>
+      <c r="C28" s="22" t="s">
+        <v>141</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E28" s="11" t="s">
         <v>29</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G28" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H28" s="11"/>
       <c r="I28" s="11"/>
@@ -1985,18 +1985,18 @@
       <c r="L28" s="12"/>
     </row>
     <row r="29" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="31"/>
-      <c r="B29" s="32"/>
-      <c r="C29" s="65"/>
+      <c r="A29" s="53"/>
+      <c r="B29" s="54"/>
+      <c r="C29" s="23"/>
       <c r="D29" s="15"/>
       <c r="E29" s="15" t="s">
         <v>30</v>
       </c>
       <c r="F29" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G29" s="15" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H29" s="15"/>
       <c r="I29" s="15"/>
@@ -2005,18 +2005,18 @@
       <c r="L29" s="16"/>
     </row>
     <row r="30" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="31"/>
-      <c r="B30" s="32"/>
-      <c r="C30" s="65"/>
+      <c r="A30" s="53"/>
+      <c r="B30" s="54"/>
+      <c r="C30" s="23"/>
       <c r="D30" s="15"/>
       <c r="E30" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F30" s="15" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G30" s="15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H30" s="15"/>
       <c r="I30" s="15"/>
@@ -2025,18 +2025,18 @@
       <c r="L30" s="16"/>
     </row>
     <row r="31" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="29"/>
-      <c r="B31" s="30"/>
-      <c r="C31" s="66"/>
+      <c r="A31" s="43"/>
+      <c r="B31" s="44"/>
+      <c r="C31" s="24"/>
       <c r="D31" s="13"/>
       <c r="E31" s="13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F31" s="13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G31" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H31" s="13"/>
       <c r="I31" s="13"/>
@@ -2045,135 +2045,135 @@
       <c r="L31" s="14"/>
     </row>
     <row r="32" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="44" t="s">
-        <v>93</v>
-      </c>
-      <c r="B32" s="45"/>
-      <c r="C32" s="45"/>
-      <c r="D32" s="45"/>
-      <c r="E32" s="45"/>
-      <c r="F32" s="45"/>
-      <c r="G32" s="45"/>
-      <c r="H32" s="45"/>
-      <c r="I32" s="45"/>
-      <c r="J32" s="45"/>
-      <c r="K32" s="45"/>
-      <c r="L32" s="46"/>
+      <c r="A32" s="63" t="s">
+        <v>91</v>
+      </c>
+      <c r="B32" s="64"/>
+      <c r="C32" s="64"/>
+      <c r="D32" s="64"/>
+      <c r="E32" s="64"/>
+      <c r="F32" s="64"/>
+      <c r="G32" s="64"/>
+      <c r="H32" s="64"/>
+      <c r="I32" s="64"/>
+      <c r="J32" s="64"/>
+      <c r="K32" s="64"/>
+      <c r="L32" s="65"/>
     </row>
     <row r="33" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="47"/>
-      <c r="B33" s="48"/>
-      <c r="C33" s="48"/>
-      <c r="D33" s="48"/>
-      <c r="E33" s="48"/>
-      <c r="F33" s="48"/>
-      <c r="G33" s="48"/>
-      <c r="H33" s="48"/>
-      <c r="I33" s="48"/>
-      <c r="J33" s="48"/>
-      <c r="K33" s="48"/>
-      <c r="L33" s="49"/>
+      <c r="A33" s="66"/>
+      <c r="B33" s="67"/>
+      <c r="C33" s="67"/>
+      <c r="D33" s="67"/>
+      <c r="E33" s="67"/>
+      <c r="F33" s="67"/>
+      <c r="G33" s="67"/>
+      <c r="H33" s="67"/>
+      <c r="I33" s="67"/>
+      <c r="J33" s="67"/>
+      <c r="K33" s="67"/>
+      <c r="L33" s="68"/>
     </row>
     <row r="34" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="33" t="s">
-        <v>76</v>
-      </c>
-      <c r="B34" s="34"/>
-      <c r="C34" s="69" t="s">
-        <v>143</v>
+      <c r="A34" s="45" t="s">
+        <v>75</v>
+      </c>
+      <c r="B34" s="46"/>
+      <c r="C34" s="27" t="s">
+        <v>141</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H34" s="1"/>
       <c r="I34" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="J34" s="1"/>
       <c r="K34" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L34" s="2"/>
     </row>
     <row r="35" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="41"/>
-      <c r="B35" s="42"/>
-      <c r="C35" s="74"/>
+      <c r="A35" s="69"/>
+      <c r="B35" s="70"/>
+      <c r="C35" s="32"/>
       <c r="D35" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E35" t="s">
-        <v>35</v>
+        <v>160</v>
       </c>
       <c r="F35" t="s">
+        <v>78</v>
+      </c>
+      <c r="I35" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="J35" t="s">
+        <v>150</v>
+      </c>
+      <c r="K35" t="s">
+        <v>53</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="69"/>
+      <c r="B36" s="70"/>
+      <c r="C36" s="32"/>
+      <c r="E36" t="s">
+        <v>89</v>
+      </c>
+      <c r="I36" t="s">
+        <v>148</v>
+      </c>
+      <c r="J36" t="s">
         <v>80</v>
-      </c>
-      <c r="I35" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="J35" t="s">
-        <v>152</v>
-      </c>
-      <c r="K35" t="s">
-        <v>54</v>
-      </c>
-      <c r="L35" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="41"/>
-      <c r="B36" s="42"/>
-      <c r="C36" s="74"/>
-      <c r="E36" t="s">
-        <v>91</v>
-      </c>
-      <c r="I36" t="s">
-        <v>150</v>
-      </c>
-      <c r="J36" t="s">
-        <v>82</v>
       </c>
       <c r="K36" t="s">
         <v>29</v>
       </c>
       <c r="L36" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="37" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="41"/>
-      <c r="B37" s="42"/>
-      <c r="C37" s="74"/>
+      <c r="A37" s="69"/>
+      <c r="B37" s="70"/>
+      <c r="C37" s="32"/>
       <c r="I37" s="9" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J37" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K37" t="s">
         <v>30</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="38" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="41"/>
-      <c r="B38" s="42"/>
-      <c r="C38" s="74"/>
+      <c r="A38" s="69"/>
+      <c r="B38" s="70"/>
+      <c r="C38" s="32"/>
       <c r="L38" s="3"/>
     </row>
     <row r="39" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="35"/>
-      <c r="B39" s="36"/>
-      <c r="C39" s="70"/>
+      <c r="A39" s="47"/>
+      <c r="B39" s="48"/>
+      <c r="C39" s="28"/>
       <c r="D39" s="6"/>
       <c r="E39" s="6"/>
       <c r="F39" s="6"/>
@@ -2185,109 +2185,96 @@
       <c r="L39" s="7"/>
     </row>
     <row r="40" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="21" t="s">
-        <v>87</v>
-      </c>
-      <c r="B40" s="22"/>
-      <c r="C40" s="67" t="s">
-        <v>143</v>
+      <c r="A40" s="37" t="s">
+        <v>85</v>
+      </c>
+      <c r="B40" s="38"/>
+      <c r="C40" s="25" t="s">
+        <v>141</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E40" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G40" s="1" t="s">
         <v>77</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H40" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I40" s="1" t="s">
-        <v>79</v>
       </c>
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
       <c r="L40" s="2"/>
     </row>
     <row r="41" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="23"/>
-      <c r="B41" s="24"/>
-      <c r="C41" s="75"/>
+      <c r="A41" s="71"/>
+      <c r="B41" s="72"/>
+      <c r="C41" s="33"/>
       <c r="E41" t="s">
-        <v>35</v>
+        <v>160</v>
       </c>
       <c r="F41" t="s">
-        <v>35</v>
+        <v>88</v>
       </c>
       <c r="G41" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H41" t="s">
-        <v>90</v>
-      </c>
-      <c r="I41" t="s">
-        <v>80</v>
+        <v>161</v>
       </c>
       <c r="L41" s="3"/>
     </row>
     <row r="42" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="25"/>
-      <c r="B42" s="26"/>
-      <c r="C42" s="68"/>
+      <c r="A42" s="39"/>
+      <c r="B42" s="40"/>
+      <c r="C42" s="26"/>
       <c r="D42" s="6"/>
       <c r="E42" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="F42" s="6" t="s">
-        <v>91</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="F42" s="6"/>
       <c r="G42" s="6"/>
-      <c r="H42" s="6"/>
-      <c r="I42" s="6"/>
       <c r="J42" s="6"/>
       <c r="K42" s="6"/>
       <c r="L42" s="7"/>
     </row>
     <row r="43" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="56" t="s">
-        <v>96</v>
-      </c>
-      <c r="B43" s="57"/>
-      <c r="C43" s="57"/>
-      <c r="D43" s="57"/>
-      <c r="E43" s="57"/>
-      <c r="F43" s="57"/>
-      <c r="G43" s="57"/>
-      <c r="H43" s="57"/>
-      <c r="I43" s="57"/>
-      <c r="J43" s="57"/>
-      <c r="K43" s="57"/>
-      <c r="L43" s="58"/>
+      <c r="A43" s="73" t="s">
+        <v>94</v>
+      </c>
+      <c r="B43" s="74"/>
+      <c r="C43" s="74"/>
+      <c r="D43" s="74"/>
+      <c r="E43" s="74"/>
+      <c r="F43" s="74"/>
+      <c r="G43" s="74"/>
+      <c r="H43" s="74"/>
+      <c r="I43" s="74"/>
+      <c r="J43" s="74"/>
+      <c r="K43" s="74"/>
+      <c r="L43" s="75"/>
     </row>
     <row r="44" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="59"/>
-      <c r="B44" s="60"/>
-      <c r="C44" s="60"/>
-      <c r="D44" s="60"/>
-      <c r="E44" s="60"/>
-      <c r="F44" s="60"/>
-      <c r="G44" s="60"/>
-      <c r="H44" s="60"/>
-      <c r="I44" s="60"/>
-      <c r="J44" s="60"/>
-      <c r="K44" s="60"/>
-      <c r="L44" s="61"/>
+      <c r="A44" s="76"/>
+      <c r="B44" s="77"/>
+      <c r="C44" s="77"/>
+      <c r="D44" s="77"/>
+      <c r="E44" s="77"/>
+      <c r="F44" s="77"/>
+      <c r="G44" s="77"/>
+      <c r="H44" s="77"/>
+      <c r="I44" s="77"/>
+      <c r="J44" s="77"/>
+      <c r="K44" s="77"/>
+      <c r="L44" s="78"/>
     </row>
     <row r="45" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="33" t="s">
-        <v>97</v>
-      </c>
-      <c r="B45" s="34"/>
+      <c r="A45" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="B45" s="46"/>
       <c r="C45" s="8" t="s">
         <v>17</v>
       </c>
@@ -2315,10 +2302,10 @@
       <c r="L45" s="2"/>
     </row>
     <row r="46" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="35"/>
-      <c r="B46" s="36"/>
-      <c r="C46" s="74" t="s">
-        <v>143</v>
+      <c r="A46" s="47"/>
+      <c r="B46" s="48"/>
+      <c r="C46" s="32" t="s">
+        <v>141</v>
       </c>
       <c r="D46" s="5" t="s">
         <v>25</v>
@@ -2347,24 +2334,24 @@
       <c r="L46" s="7"/>
     </row>
     <row r="47" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="33" t="s">
-        <v>98</v>
-      </c>
-      <c r="B47" s="34"/>
-      <c r="C47" s="69" t="s">
-        <v>143</v>
+      <c r="A47" s="45" t="s">
+        <v>96</v>
+      </c>
+      <c r="B47" s="46"/>
+      <c r="C47" s="27" t="s">
+        <v>141</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>34</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H47" s="1" t="s">
         <v>15</v>
@@ -2377,9 +2364,9 @@
       <c r="L47" s="2"/>
     </row>
     <row r="48" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="35"/>
-      <c r="B48" s="36"/>
-      <c r="C48" s="70"/>
+      <c r="A48" s="47"/>
+      <c r="B48" s="48"/>
+      <c r="C48" s="28"/>
       <c r="D48" s="6" t="s">
         <v>25</v>
       </c>
@@ -2387,40 +2374,40 @@
         <v>4</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="J48" s="6"/>
       <c r="K48" s="6"/>
       <c r="L48" s="7"/>
     </row>
     <row r="49" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="33" t="s">
-        <v>102</v>
-      </c>
-      <c r="B49" s="34"/>
-      <c r="C49" s="69" t="s">
-        <v>143</v>
+      <c r="A49" s="45" t="s">
+        <v>100</v>
+      </c>
+      <c r="B49" s="46"/>
+      <c r="C49" s="27" t="s">
+        <v>141</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>34</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H49" s="1" t="s">
         <v>15</v>
@@ -2433,9 +2420,9 @@
       <c r="L49" s="2"/>
     </row>
     <row r="50" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="35"/>
-      <c r="B50" s="36"/>
-      <c r="C50" s="70"/>
+      <c r="A50" s="47"/>
+      <c r="B50" s="48"/>
+      <c r="C50" s="28"/>
       <c r="D50" s="6" t="s">
         <v>25</v>
       </c>
@@ -2443,34 +2430,34 @@
         <v>4</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="J50" s="6"/>
       <c r="K50" s="6"/>
       <c r="L50" s="7"/>
     </row>
     <row r="51" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="21" t="s">
-        <v>103</v>
-      </c>
-      <c r="B51" s="22"/>
-      <c r="C51" s="67" t="s">
-        <v>143</v>
+      <c r="A51" s="37" t="s">
+        <v>101</v>
+      </c>
+      <c r="B51" s="38"/>
+      <c r="C51" s="25" t="s">
+        <v>141</v>
       </c>
       <c r="D51" s="8" t="s">
         <v>39</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
@@ -2481,9 +2468,9 @@
       <c r="L51" s="2"/>
     </row>
     <row r="52" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="25"/>
-      <c r="B52" s="26"/>
-      <c r="C52" s="68"/>
+      <c r="A52" s="39"/>
+      <c r="B52" s="40"/>
+      <c r="C52" s="26"/>
       <c r="D52" s="5"/>
       <c r="E52" s="6" t="s">
         <v>36</v>
@@ -2497,18 +2484,18 @@
       <c r="L52" s="7"/>
     </row>
     <row r="53" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="B53" s="22"/>
-      <c r="C53" s="67" t="s">
-        <v>143</v>
+      <c r="A53" s="37" t="s">
+        <v>102</v>
+      </c>
+      <c r="B53" s="38"/>
+      <c r="C53" s="25" t="s">
+        <v>141</v>
       </c>
       <c r="D53" s="8" t="s">
         <v>42</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F53" s="1"/>
       <c r="H53" s="1"/>
@@ -2518,9 +2505,9 @@
       <c r="L53" s="2"/>
     </row>
     <row r="54" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="25"/>
-      <c r="B54" s="26"/>
-      <c r="C54" s="68"/>
+      <c r="A54" s="39"/>
+      <c r="B54" s="40"/>
+      <c r="C54" s="26"/>
       <c r="D54" s="5"/>
       <c r="E54" s="6" t="s">
         <v>40</v>
@@ -2533,18 +2520,18 @@
       <c r="L54" s="7"/>
     </row>
     <row r="55" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="21" t="s">
-        <v>105</v>
-      </c>
-      <c r="B55" s="22"/>
-      <c r="C55" s="71" t="s">
-        <v>143</v>
+      <c r="A55" s="37" t="s">
+        <v>103</v>
+      </c>
+      <c r="B55" s="38"/>
+      <c r="C55" s="29" t="s">
+        <v>141</v>
       </c>
       <c r="D55" s="8" t="s">
         <v>44</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
@@ -2555,9 +2542,9 @@
       <c r="L55" s="2"/>
     </row>
     <row r="56" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="25"/>
-      <c r="B56" s="26"/>
-      <c r="C56" s="72"/>
+      <c r="A56" s="39"/>
+      <c r="B56" s="40"/>
+      <c r="C56" s="30"/>
       <c r="D56" s="5"/>
       <c r="E56" s="6" t="s">
         <v>40</v>
@@ -2570,21 +2557,21 @@
       <c r="L56" s="7"/>
     </row>
     <row r="57" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="27" t="s">
-        <v>106</v>
-      </c>
-      <c r="B57" s="28"/>
-      <c r="C57" s="64" t="s">
-        <v>143</v>
+      <c r="A57" s="41" t="s">
+        <v>104</v>
+      </c>
+      <c r="B57" s="42"/>
+      <c r="C57" s="22" t="s">
+        <v>141</v>
       </c>
       <c r="D57" s="17" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G57" s="11"/>
       <c r="H57" s="11"/>
@@ -2594,15 +2581,15 @@
       <c r="L57" s="12"/>
     </row>
     <row r="58" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="29"/>
-      <c r="B58" s="30"/>
-      <c r="C58" s="66"/>
+      <c r="A58" s="43"/>
+      <c r="B58" s="44"/>
+      <c r="C58" s="24"/>
       <c r="D58" s="18"/>
       <c r="E58" s="13" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F58" s="13" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G58" s="13"/>
       <c r="H58" s="13"/>
@@ -2612,47 +2599,47 @@
       <c r="L58" s="14"/>
     </row>
     <row r="59" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="21" t="s">
+      <c r="A59" s="37" t="s">
+        <v>133</v>
+      </c>
+      <c r="B59" s="38"/>
+      <c r="C59" s="33" t="s">
+        <v>141</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="E59" t="s">
+        <v>140</v>
+      </c>
+      <c r="I59" t="s">
         <v>135</v>
       </c>
-      <c r="B59" s="22"/>
-      <c r="C59" s="75" t="s">
-        <v>143</v>
-      </c>
-      <c r="D59" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="E59" t="s">
-        <v>142</v>
-      </c>
-      <c r="I59" t="s">
-        <v>137</v>
-      </c>
       <c r="L59" s="3"/>
     </row>
     <row r="60" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="25"/>
-      <c r="B60" s="26"/>
-      <c r="C60" s="75"/>
+      <c r="A60" s="39"/>
+      <c r="B60" s="40"/>
+      <c r="C60" s="33"/>
       <c r="D60" s="4"/>
       <c r="I60" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="L60" s="3"/>
     </row>
     <row r="61" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="27" t="s">
-        <v>108</v>
-      </c>
-      <c r="B61" s="28"/>
-      <c r="C61" s="64" t="s">
-        <v>143</v>
+      <c r="A61" s="41" t="s">
+        <v>106</v>
+      </c>
+      <c r="B61" s="42"/>
+      <c r="C61" s="22" t="s">
+        <v>141</v>
       </c>
       <c r="D61" s="17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F61" s="11"/>
       <c r="G61" s="11"/>
@@ -2663,9 +2650,9 @@
       <c r="L61" s="12"/>
     </row>
     <row r="62" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="29"/>
-      <c r="B62" s="30"/>
-      <c r="C62" s="66"/>
+      <c r="A62" s="43"/>
+      <c r="B62" s="44"/>
+      <c r="C62" s="24"/>
       <c r="D62" s="18"/>
       <c r="E62" s="13"/>
       <c r="F62" s="13"/>
@@ -2677,18 +2664,18 @@
       <c r="L62" s="14"/>
     </row>
     <row r="63" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="27" t="s">
-        <v>107</v>
-      </c>
-      <c r="B63" s="28"/>
-      <c r="C63" s="64" t="s">
-        <v>143</v>
+      <c r="A63" s="41" t="s">
+        <v>105</v>
+      </c>
+      <c r="B63" s="42"/>
+      <c r="C63" s="22" t="s">
+        <v>141</v>
       </c>
       <c r="D63" s="17" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F63" s="11"/>
       <c r="G63" s="11"/>
@@ -2699,9 +2686,9 @@
       <c r="L63" s="12"/>
     </row>
     <row r="64" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="29"/>
-      <c r="B64" s="30"/>
-      <c r="C64" s="66"/>
+      <c r="A64" s="43"/>
+      <c r="B64" s="44"/>
+      <c r="C64" s="24"/>
       <c r="D64" s="18"/>
       <c r="E64" s="13"/>
       <c r="F64" s="13"/>
@@ -2713,24 +2700,24 @@
       <c r="L64" s="14"/>
     </row>
     <row r="65" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="27" t="s">
-        <v>109</v>
-      </c>
-      <c r="B65" s="28"/>
-      <c r="C65" s="64" t="s">
-        <v>143</v>
+      <c r="A65" s="41" t="s">
+        <v>107</v>
+      </c>
+      <c r="B65" s="42"/>
+      <c r="C65" s="22" t="s">
+        <v>141</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G65" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H65" s="11"/>
       <c r="I65" s="11"/>
@@ -2739,18 +2726,18 @@
       <c r="L65" s="12"/>
     </row>
     <row r="66" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="31"/>
-      <c r="B66" s="32"/>
-      <c r="C66" s="65"/>
+      <c r="A66" s="53"/>
+      <c r="B66" s="54"/>
+      <c r="C66" s="23"/>
       <c r="D66" s="15"/>
       <c r="E66" s="15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F66" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G66" s="15" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H66" s="15"/>
       <c r="I66" s="15"/>
@@ -2759,18 +2746,18 @@
       <c r="L66" s="16"/>
     </row>
     <row r="67" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="31"/>
-      <c r="B67" s="32"/>
-      <c r="C67" s="65"/>
+      <c r="A67" s="53"/>
+      <c r="B67" s="54"/>
+      <c r="C67" s="23"/>
       <c r="D67" s="15"/>
       <c r="E67" s="15" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F67" s="15" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G67" s="15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H67" s="15"/>
       <c r="I67" s="15"/>
@@ -2779,18 +2766,18 @@
       <c r="L67" s="16"/>
     </row>
     <row r="68" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="29"/>
-      <c r="B68" s="30"/>
-      <c r="C68" s="66"/>
+      <c r="A68" s="43"/>
+      <c r="B68" s="44"/>
+      <c r="C68" s="24"/>
       <c r="D68" s="13"/>
       <c r="E68" s="13" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F68" s="13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G68" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H68" s="13"/>
       <c r="I68" s="13"/>
@@ -2799,75 +2786,75 @@
       <c r="L68" s="14"/>
     </row>
     <row r="69" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="27" t="s">
+      <c r="A69" s="41" t="s">
+        <v>112</v>
+      </c>
+      <c r="B69" s="42"/>
+      <c r="C69" s="22" t="s">
+        <v>141</v>
+      </c>
+      <c r="D69" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="E69" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="B69" s="28"/>
-      <c r="C69" s="64" t="s">
-        <v>143</v>
-      </c>
-      <c r="D69" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="E69" s="11" t="s">
-        <v>116</v>
-      </c>
       <c r="F69" s="11" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G69" s="11" t="s">
         <v>35</v>
       </c>
       <c r="H69" s="11" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I69" s="11" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="J69" s="11"/>
       <c r="K69" s="11"/>
       <c r="L69" s="12"/>
     </row>
     <row r="70" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="31"/>
-      <c r="B70" s="32"/>
-      <c r="C70" s="65"/>
+      <c r="A70" s="53"/>
+      <c r="B70" s="54"/>
+      <c r="C70" s="23"/>
       <c r="D70" s="19"/>
       <c r="E70" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F70" s="15" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G70" s="15" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="H70" s="15" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I70" s="15" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="J70" s="15"/>
       <c r="K70" s="15"/>
       <c r="L70" s="16"/>
     </row>
     <row r="71" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="31"/>
-      <c r="B71" s="32"/>
-      <c r="C71" s="65"/>
+      <c r="A71" s="53"/>
+      <c r="B71" s="54"/>
+      <c r="C71" s="23"/>
       <c r="D71" s="19"/>
       <c r="E71" s="15" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F71" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="G71" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="G71" s="15" t="s">
+      <c r="H71" s="15" t="s">
         <v>121</v>
-      </c>
-      <c r="H71" s="15" t="s">
-        <v>123</v>
       </c>
       <c r="I71" s="15"/>
       <c r="J71" s="15"/>
@@ -2875,17 +2862,17 @@
       <c r="L71" s="16"/>
     </row>
     <row r="72" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="29"/>
-      <c r="B72" s="30"/>
-      <c r="C72" s="66"/>
+      <c r="A72" s="43"/>
+      <c r="B72" s="44"/>
+      <c r="C72" s="24"/>
       <c r="D72" s="18"/>
       <c r="E72" s="13" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F72" s="13"/>
       <c r="G72" s="13"/>
       <c r="H72" s="13" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I72" s="15"/>
       <c r="J72" s="13"/>
@@ -2893,75 +2880,75 @@
       <c r="L72" s="14"/>
     </row>
     <row r="73" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="21" t="s">
-        <v>127</v>
-      </c>
-      <c r="B73" s="22"/>
-      <c r="C73" s="67" t="s">
-        <v>143</v>
+      <c r="A73" s="37" t="s">
+        <v>125</v>
+      </c>
+      <c r="B73" s="38"/>
+      <c r="C73" s="25" t="s">
+        <v>141</v>
       </c>
       <c r="D73" s="8" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="I73" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J73" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="L73" s="2"/>
     </row>
     <row r="74" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="23"/>
-      <c r="B74" s="24"/>
-      <c r="C74" s="75"/>
+      <c r="A74" s="71"/>
+      <c r="B74" s="72"/>
+      <c r="C74" s="33"/>
       <c r="D74" s="4"/>
       <c r="E74" t="s">
+        <v>128</v>
+      </c>
+      <c r="F74" t="s">
+        <v>129</v>
+      </c>
+      <c r="G74" t="s">
+        <v>147</v>
+      </c>
+      <c r="H74" t="s">
+        <v>147</v>
+      </c>
+      <c r="I74" t="s">
+        <v>142</v>
+      </c>
+      <c r="J74" t="s">
+        <v>159</v>
+      </c>
+      <c r="L74" s="3"/>
+    </row>
+    <row r="75" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="71"/>
+      <c r="B75" s="72"/>
+      <c r="C75" s="33"/>
+      <c r="D75" s="5"/>
+      <c r="E75" s="80" t="s">
         <v>130</v>
       </c>
-      <c r="F74" t="s">
-        <v>131</v>
-      </c>
-      <c r="G74" t="s">
-        <v>149</v>
-      </c>
-      <c r="H74" t="s">
-        <v>149</v>
-      </c>
-      <c r="I74" t="s">
-        <v>144</v>
-      </c>
-      <c r="J74" t="s">
-        <v>161</v>
-      </c>
-      <c r="L74" s="3"/>
-    </row>
-    <row r="75" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="23"/>
-      <c r="B75" s="24"/>
-      <c r="C75" s="75"/>
-      <c r="D75" s="5"/>
-      <c r="E75" s="20" t="s">
-        <v>132</v>
-      </c>
-      <c r="F75" s="20"/>
+      <c r="F75" s="80"/>
       <c r="G75" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="H75" s="6" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="I75" s="6"/>
       <c r="J75" s="6"/>
@@ -2969,75 +2956,75 @@
       <c r="L75" s="7"/>
     </row>
     <row r="76" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="23"/>
-      <c r="B76" s="24"/>
-      <c r="C76" s="75" t="s">
-        <v>143</v>
+      <c r="A76" s="71"/>
+      <c r="B76" s="72"/>
+      <c r="C76" s="33" t="s">
+        <v>141</v>
       </c>
       <c r="D76" s="8" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H76" s="1" t="s">
         <v>35</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="J76" s="1"/>
       <c r="K76" s="1"/>
       <c r="L76" s="2"/>
     </row>
     <row r="77" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="23"/>
-      <c r="B77" s="24"/>
-      <c r="C77" s="75"/>
+      <c r="A77" s="71"/>
+      <c r="B77" s="72"/>
+      <c r="C77" s="33"/>
       <c r="D77" s="4"/>
       <c r="E77" t="s">
+        <v>157</v>
+      </c>
+      <c r="F77" t="s">
+        <v>158</v>
+      </c>
+      <c r="G77" t="s">
+        <v>77</v>
+      </c>
+      <c r="H77" t="s">
+        <v>118</v>
+      </c>
+      <c r="I77" t="s">
         <v>159</v>
       </c>
-      <c r="F77" t="s">
-        <v>160</v>
-      </c>
-      <c r="G77" t="s">
-        <v>79</v>
-      </c>
-      <c r="H77" t="s">
-        <v>120</v>
-      </c>
-      <c r="I77" t="s">
-        <v>161</v>
-      </c>
       <c r="L77" s="3"/>
     </row>
     <row r="78" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="23"/>
-      <c r="B78" s="24"/>
-      <c r="C78" s="75"/>
+      <c r="A78" s="71"/>
+      <c r="B78" s="72"/>
+      <c r="C78" s="33"/>
       <c r="D78" s="5"/>
-      <c r="E78" s="20" t="s">
-        <v>133</v>
-      </c>
-      <c r="F78" s="20"/>
-      <c r="G78" s="20"/>
-      <c r="H78" s="20"/>
+      <c r="E78" s="80" t="s">
+        <v>131</v>
+      </c>
+      <c r="F78" s="80"/>
+      <c r="G78" s="80"/>
+      <c r="H78" s="80"/>
       <c r="I78" s="6"/>
       <c r="J78" s="6"/>
       <c r="K78" s="6"/>
       <c r="L78" s="7"/>
     </row>
     <row r="79" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="23"/>
-      <c r="B79" s="24"/>
-      <c r="C79" s="75"/>
+      <c r="A79" s="71"/>
+      <c r="B79" s="72"/>
+      <c r="C79" s="33"/>
       <c r="D79" s="8"/>
       <c r="H79" s="1"/>
       <c r="I79" s="1"/>
@@ -3046,16 +3033,16 @@
       <c r="L79" s="2"/>
     </row>
     <row r="80" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="23"/>
-      <c r="B80" s="24"/>
-      <c r="C80" s="75"/>
+      <c r="A80" s="71"/>
+      <c r="B80" s="72"/>
+      <c r="C80" s="33"/>
       <c r="D80" s="4"/>
       <c r="L80" s="3"/>
     </row>
     <row r="81" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="25"/>
-      <c r="B81" s="26"/>
-      <c r="C81" s="68"/>
+      <c r="A81" s="39"/>
+      <c r="B81" s="40"/>
+      <c r="C81" s="26"/>
       <c r="D81" s="5"/>
       <c r="E81" s="6"/>
       <c r="F81" s="6"/>
@@ -3068,31 +3055,8 @@
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="A51:B52"/>
-    <mergeCell ref="A53:B54"/>
-    <mergeCell ref="A55:B56"/>
-    <mergeCell ref="A57:B58"/>
-    <mergeCell ref="A59:B60"/>
-    <mergeCell ref="A12:B13"/>
-    <mergeCell ref="A14:B15"/>
-    <mergeCell ref="A16:B17"/>
-    <mergeCell ref="A18:B19"/>
-    <mergeCell ref="A20:B21"/>
-    <mergeCell ref="A4:B5"/>
-    <mergeCell ref="A6:B7"/>
-    <mergeCell ref="A8:B11"/>
-    <mergeCell ref="A2:L3"/>
-    <mergeCell ref="A22:B23"/>
-    <mergeCell ref="A24:B25"/>
-    <mergeCell ref="A26:L27"/>
-    <mergeCell ref="A28:B31"/>
-    <mergeCell ref="A32:L33"/>
-    <mergeCell ref="A34:B39"/>
-    <mergeCell ref="A40:B42"/>
-    <mergeCell ref="A45:B46"/>
-    <mergeCell ref="A43:L44"/>
-    <mergeCell ref="O6:P6"/>
-    <mergeCell ref="O8:P8"/>
+    <mergeCell ref="G78:H78"/>
+    <mergeCell ref="A73:B81"/>
     <mergeCell ref="A47:B48"/>
     <mergeCell ref="A49:B50"/>
     <mergeCell ref="E75:F75"/>
@@ -3101,8 +3065,31 @@
     <mergeCell ref="A63:B64"/>
     <mergeCell ref="A65:B68"/>
     <mergeCell ref="A69:B72"/>
-    <mergeCell ref="G78:H78"/>
-    <mergeCell ref="A73:B81"/>
+    <mergeCell ref="A40:B42"/>
+    <mergeCell ref="A45:B46"/>
+    <mergeCell ref="A43:L44"/>
+    <mergeCell ref="O6:P6"/>
+    <mergeCell ref="O8:P8"/>
+    <mergeCell ref="A24:B25"/>
+    <mergeCell ref="A26:L27"/>
+    <mergeCell ref="A28:B31"/>
+    <mergeCell ref="A32:L33"/>
+    <mergeCell ref="A34:B39"/>
+    <mergeCell ref="A4:B5"/>
+    <mergeCell ref="A6:B7"/>
+    <mergeCell ref="A8:B11"/>
+    <mergeCell ref="A2:L3"/>
+    <mergeCell ref="A22:B23"/>
+    <mergeCell ref="A12:B13"/>
+    <mergeCell ref="A14:B15"/>
+    <mergeCell ref="A16:B17"/>
+    <mergeCell ref="A18:B19"/>
+    <mergeCell ref="A20:B21"/>
+    <mergeCell ref="A51:B52"/>
+    <mergeCell ref="A53:B54"/>
+    <mergeCell ref="A55:B56"/>
+    <mergeCell ref="A57:B58"/>
+    <mergeCell ref="A59:B60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Can Register Map.xlsx
+++ b/Can Register Map.xlsx
@@ -844,18 +844,39 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -868,17 +889,32 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -892,89 +928,53 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1318,43 +1318,43 @@
       <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="55" t="s">
+      <c r="A2" s="79" t="s">
         <v>93</v>
       </c>
-      <c r="B2" s="55"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
-      <c r="L2" s="56"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
+      <c r="J2" s="79"/>
+      <c r="K2" s="79"/>
+      <c r="L2" s="80"/>
     </row>
     <row r="3" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="57"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="57"/>
-      <c r="L3" s="58"/>
+      <c r="A3" s="69"/>
+      <c r="B3" s="69"/>
+      <c r="C3" s="69"/>
+      <c r="D3" s="69"/>
+      <c r="E3" s="69"/>
+      <c r="F3" s="69"/>
+      <c r="G3" s="69"/>
+      <c r="H3" s="69"/>
+      <c r="I3" s="69"/>
+      <c r="J3" s="69"/>
+      <c r="K3" s="69"/>
+      <c r="L3" s="70"/>
       <c r="O3" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="49" t="s">
+      <c r="A4" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="50"/>
+      <c r="B4" s="62"/>
       <c r="C4" s="11" t="s">
         <v>17</v>
       </c>
@@ -1383,8 +1383,8 @@
       <c r="L4" s="12"/>
     </row>
     <row r="5" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="51"/>
-      <c r="B5" s="52"/>
+      <c r="A5" s="63"/>
+      <c r="B5" s="64"/>
       <c r="C5" s="21" t="s">
         <v>141</v>
       </c>
@@ -1413,10 +1413,10 @@
       <c r="L5" s="14"/>
     </row>
     <row r="6" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="49" t="s">
+      <c r="A6" s="61" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="50"/>
+      <c r="B6" s="62"/>
       <c r="C6" s="20" t="s">
         <v>141</v>
       </c>
@@ -1447,13 +1447,13 @@
       <c r="L6" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="O6" s="79"/>
-      <c r="P6" s="79"/>
+      <c r="O6" s="60"/>
+      <c r="P6" s="60"/>
       <c r="Q6" s="10"/>
     </row>
     <row r="7" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="51"/>
-      <c r="B7" s="52"/>
+      <c r="A7" s="63"/>
+      <c r="B7" s="64"/>
       <c r="C7" s="21"/>
       <c r="D7" s="13"/>
       <c r="E7" s="13" t="s">
@@ -1482,10 +1482,10 @@
       </c>
     </row>
     <row r="8" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="41" t="s">
+      <c r="A8" s="48" t="s">
         <v>48</v>
       </c>
-      <c r="B8" s="42"/>
+      <c r="B8" s="49"/>
       <c r="C8" s="22" t="s">
         <v>141</v>
       </c>
@@ -1506,15 +1506,15 @@
       <c r="J8" s="11"/>
       <c r="K8" s="11"/>
       <c r="L8" s="12"/>
-      <c r="O8" s="79" t="s">
+      <c r="O8" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="P8" s="79"/>
+      <c r="P8" s="60"/>
       <c r="Q8" s="10"/>
     </row>
     <row r="9" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="53"/>
-      <c r="B9" s="54"/>
+      <c r="A9" s="52"/>
+      <c r="B9" s="53"/>
       <c r="C9" s="23"/>
       <c r="D9" s="15" t="s">
         <v>54</v>
@@ -1556,8 +1556,8 @@
       </c>
     </row>
     <row r="10" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="53"/>
-      <c r="B10" s="54"/>
+      <c r="A10" s="52"/>
+      <c r="B10" s="53"/>
       <c r="C10" s="23"/>
       <c r="D10" s="15" t="s">
         <v>55</v>
@@ -1599,8 +1599,8 @@
       </c>
     </row>
     <row r="11" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="43"/>
-      <c r="B11" s="44"/>
+      <c r="A11" s="50"/>
+      <c r="B11" s="51"/>
       <c r="C11" s="24"/>
       <c r="D11" s="13" t="s">
         <v>57</v>
@@ -1642,10 +1642,10 @@
       </c>
     </row>
     <row r="12" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="37" t="s">
+      <c r="A12" s="38" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="38"/>
+      <c r="B12" s="39"/>
       <c r="C12" s="25" t="s">
         <v>141</v>
       </c>
@@ -1674,8 +1674,8 @@
       <c r="L12" s="2"/>
     </row>
     <row r="13" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="39"/>
-      <c r="B13" s="40"/>
+      <c r="A13" s="42"/>
+      <c r="B13" s="43"/>
       <c r="C13" s="26"/>
       <c r="D13" s="6"/>
       <c r="E13" s="6" t="s">
@@ -1694,10 +1694,10 @@
       </c>
     </row>
     <row r="14" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="45" t="s">
+      <c r="A14" s="44" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="46"/>
+      <c r="B14" s="45"/>
       <c r="C14" s="27" t="s">
         <v>141</v>
       </c>
@@ -1716,8 +1716,8 @@
       <c r="L14" s="2"/>
     </row>
     <row r="15" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="47"/>
-      <c r="B15" s="48"/>
+      <c r="A15" s="46"/>
+      <c r="B15" s="47"/>
       <c r="C15" s="28"/>
       <c r="D15" s="6"/>
       <c r="E15" s="6" t="s">
@@ -1734,10 +1734,10 @@
       <c r="L15" s="7"/>
     </row>
     <row r="16" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="37" t="s">
+      <c r="A16" s="38" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="38"/>
+      <c r="B16" s="39"/>
       <c r="C16" s="29" t="s">
         <v>141</v>
       </c>
@@ -1756,8 +1756,8 @@
       <c r="L16" s="2"/>
     </row>
     <row r="17" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="39"/>
-      <c r="B17" s="40"/>
+      <c r="A17" s="42"/>
+      <c r="B17" s="43"/>
       <c r="C17" s="30"/>
       <c r="D17" s="6"/>
       <c r="E17" s="6" t="s">
@@ -1774,10 +1774,10 @@
       <c r="L17" s="7"/>
     </row>
     <row r="18" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="37" t="s">
+      <c r="A18" s="38" t="s">
         <v>137</v>
       </c>
-      <c r="B18" s="38"/>
+      <c r="B18" s="39"/>
       <c r="C18" s="31" t="s">
         <v>141</v>
       </c>
@@ -1795,8 +1795,8 @@
       </c>
     </row>
     <row r="19" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="39"/>
-      <c r="B19" s="40"/>
+      <c r="A19" s="42"/>
+      <c r="B19" s="43"/>
       <c r="C19" s="31"/>
       <c r="E19" t="s">
         <v>138</v>
@@ -1809,10 +1809,10 @@
       </c>
     </row>
     <row r="20" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="49" t="s">
+      <c r="A20" s="61" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="50"/>
+      <c r="B20" s="62"/>
       <c r="C20" s="20" t="s">
         <v>141</v>
       </c>
@@ -1835,8 +1835,8 @@
       </c>
     </row>
     <row r="21" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="51"/>
-      <c r="B21" s="52"/>
+      <c r="A21" s="63"/>
+      <c r="B21" s="64"/>
       <c r="C21" s="21"/>
       <c r="D21" s="13"/>
       <c r="E21" s="13" t="s">
@@ -1857,10 +1857,10 @@
       </c>
     </row>
     <row r="22" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="49" t="s">
+      <c r="A22" s="61" t="s">
         <v>58</v>
       </c>
-      <c r="B22" s="50"/>
+      <c r="B22" s="62"/>
       <c r="C22" s="20" t="s">
         <v>141</v>
       </c>
@@ -1879,8 +1879,8 @@
       <c r="L22" s="12"/>
     </row>
     <row r="23" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="51"/>
-      <c r="B23" s="52"/>
+      <c r="A23" s="63"/>
+      <c r="B23" s="64"/>
       <c r="C23" s="21"/>
       <c r="D23" s="13"/>
       <c r="E23" s="13"/>
@@ -1893,10 +1893,10 @@
       <c r="L23" s="14"/>
     </row>
     <row r="24" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="49" t="s">
+      <c r="A24" s="61" t="s">
         <v>59</v>
       </c>
-      <c r="B24" s="50"/>
+      <c r="B24" s="62"/>
       <c r="C24" s="20" t="s">
         <v>141</v>
       </c>
@@ -1915,8 +1915,8 @@
       <c r="L24" s="12"/>
     </row>
     <row r="25" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="51"/>
-      <c r="B25" s="52"/>
+      <c r="A25" s="63"/>
+      <c r="B25" s="64"/>
       <c r="C25" s="21"/>
       <c r="D25" s="13"/>
       <c r="E25" s="13"/>
@@ -1929,40 +1929,40 @@
       <c r="L25" s="14"/>
     </row>
     <row r="26" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="59" t="s">
+      <c r="A26" s="65" t="s">
         <v>92</v>
       </c>
-      <c r="B26" s="60"/>
-      <c r="C26" s="60"/>
-      <c r="D26" s="60"/>
-      <c r="E26" s="60"/>
-      <c r="F26" s="60"/>
-      <c r="G26" s="60"/>
-      <c r="H26" s="60"/>
-      <c r="I26" s="60"/>
-      <c r="J26" s="60"/>
-      <c r="K26" s="60"/>
-      <c r="L26" s="61"/>
+      <c r="B26" s="66"/>
+      <c r="C26" s="66"/>
+      <c r="D26" s="66"/>
+      <c r="E26" s="66"/>
+      <c r="F26" s="66"/>
+      <c r="G26" s="66"/>
+      <c r="H26" s="66"/>
+      <c r="I26" s="66"/>
+      <c r="J26" s="66"/>
+      <c r="K26" s="66"/>
+      <c r="L26" s="67"/>
     </row>
     <row r="27" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="62"/>
-      <c r="B27" s="57"/>
-      <c r="C27" s="57"/>
-      <c r="D27" s="57"/>
-      <c r="E27" s="57"/>
-      <c r="F27" s="57"/>
-      <c r="G27" s="57"/>
-      <c r="H27" s="57"/>
-      <c r="I27" s="57"/>
-      <c r="J27" s="57"/>
-      <c r="K27" s="57"/>
-      <c r="L27" s="58"/>
+      <c r="A27" s="68"/>
+      <c r="B27" s="69"/>
+      <c r="C27" s="69"/>
+      <c r="D27" s="69"/>
+      <c r="E27" s="69"/>
+      <c r="F27" s="69"/>
+      <c r="G27" s="69"/>
+      <c r="H27" s="69"/>
+      <c r="I27" s="69"/>
+      <c r="J27" s="69"/>
+      <c r="K27" s="69"/>
+      <c r="L27" s="70"/>
     </row>
     <row r="28" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="41" t="s">
+      <c r="A28" s="48" t="s">
         <v>60</v>
       </c>
-      <c r="B28" s="42"/>
+      <c r="B28" s="49"/>
       <c r="C28" s="22" t="s">
         <v>141</v>
       </c>
@@ -1985,8 +1985,8 @@
       <c r="L28" s="12"/>
     </row>
     <row r="29" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="53"/>
-      <c r="B29" s="54"/>
+      <c r="A29" s="52"/>
+      <c r="B29" s="53"/>
       <c r="C29" s="23"/>
       <c r="D29" s="15"/>
       <c r="E29" s="15" t="s">
@@ -2005,8 +2005,8 @@
       <c r="L29" s="16"/>
     </row>
     <row r="30" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="53"/>
-      <c r="B30" s="54"/>
+      <c r="A30" s="52"/>
+      <c r="B30" s="53"/>
       <c r="C30" s="23"/>
       <c r="D30" s="15"/>
       <c r="E30" s="15" t="s">
@@ -2025,8 +2025,8 @@
       <c r="L30" s="16"/>
     </row>
     <row r="31" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="43"/>
-      <c r="B31" s="44"/>
+      <c r="A31" s="50"/>
+      <c r="B31" s="51"/>
       <c r="C31" s="24"/>
       <c r="D31" s="13"/>
       <c r="E31" s="13" t="s">
@@ -2045,40 +2045,40 @@
       <c r="L31" s="14"/>
     </row>
     <row r="32" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="63" t="s">
+      <c r="A32" s="71" t="s">
         <v>91</v>
       </c>
-      <c r="B32" s="64"/>
-      <c r="C32" s="64"/>
-      <c r="D32" s="64"/>
-      <c r="E32" s="64"/>
-      <c r="F32" s="64"/>
-      <c r="G32" s="64"/>
-      <c r="H32" s="64"/>
-      <c r="I32" s="64"/>
-      <c r="J32" s="64"/>
-      <c r="K32" s="64"/>
-      <c r="L32" s="65"/>
+      <c r="B32" s="72"/>
+      <c r="C32" s="72"/>
+      <c r="D32" s="72"/>
+      <c r="E32" s="72"/>
+      <c r="F32" s="72"/>
+      <c r="G32" s="72"/>
+      <c r="H32" s="72"/>
+      <c r="I32" s="72"/>
+      <c r="J32" s="72"/>
+      <c r="K32" s="72"/>
+      <c r="L32" s="73"/>
     </row>
     <row r="33" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="66"/>
-      <c r="B33" s="67"/>
-      <c r="C33" s="67"/>
-      <c r="D33" s="67"/>
-      <c r="E33" s="67"/>
-      <c r="F33" s="67"/>
-      <c r="G33" s="67"/>
-      <c r="H33" s="67"/>
-      <c r="I33" s="67"/>
-      <c r="J33" s="67"/>
-      <c r="K33" s="67"/>
-      <c r="L33" s="68"/>
+      <c r="A33" s="74"/>
+      <c r="B33" s="75"/>
+      <c r="C33" s="75"/>
+      <c r="D33" s="75"/>
+      <c r="E33" s="75"/>
+      <c r="F33" s="75"/>
+      <c r="G33" s="75"/>
+      <c r="H33" s="75"/>
+      <c r="I33" s="75"/>
+      <c r="J33" s="75"/>
+      <c r="K33" s="75"/>
+      <c r="L33" s="76"/>
     </row>
     <row r="34" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="45" t="s">
+      <c r="A34" s="44" t="s">
         <v>75</v>
       </c>
-      <c r="B34" s="46"/>
+      <c r="B34" s="45"/>
       <c r="C34" s="27" t="s">
         <v>141</v>
       </c>
@@ -2102,8 +2102,8 @@
       <c r="L34" s="2"/>
     </row>
     <row r="35" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="69"/>
-      <c r="B35" s="70"/>
+      <c r="A35" s="77"/>
+      <c r="B35" s="78"/>
       <c r="C35" s="32"/>
       <c r="D35" t="s">
         <v>123</v>
@@ -2128,8 +2128,8 @@
       </c>
     </row>
     <row r="36" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="69"/>
-      <c r="B36" s="70"/>
+      <c r="A36" s="77"/>
+      <c r="B36" s="78"/>
       <c r="C36" s="32"/>
       <c r="E36" t="s">
         <v>89</v>
@@ -2148,8 +2148,8 @@
       </c>
     </row>
     <row r="37" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="69"/>
-      <c r="B37" s="70"/>
+      <c r="A37" s="77"/>
+      <c r="B37" s="78"/>
       <c r="C37" s="32"/>
       <c r="I37" s="9" t="s">
         <v>149</v>
@@ -2165,14 +2165,14 @@
       </c>
     </row>
     <row r="38" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="69"/>
-      <c r="B38" s="70"/>
+      <c r="A38" s="77"/>
+      <c r="B38" s="78"/>
       <c r="C38" s="32"/>
       <c r="L38" s="3"/>
     </row>
     <row r="39" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="47"/>
-      <c r="B39" s="48"/>
+      <c r="A39" s="46"/>
+      <c r="B39" s="47"/>
       <c r="C39" s="28"/>
       <c r="D39" s="6"/>
       <c r="E39" s="6"/>
@@ -2185,10 +2185,10 @@
       <c r="L39" s="7"/>
     </row>
     <row r="40" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="37" t="s">
+      <c r="A40" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="B40" s="38"/>
+      <c r="B40" s="39"/>
       <c r="C40" s="25" t="s">
         <v>141</v>
       </c>
@@ -2209,8 +2209,8 @@
       <c r="L40" s="2"/>
     </row>
     <row r="41" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="71"/>
-      <c r="B41" s="72"/>
+      <c r="A41" s="40"/>
+      <c r="B41" s="41"/>
       <c r="C41" s="33"/>
       <c r="E41" t="s">
         <v>160</v>
@@ -2227,8 +2227,8 @@
       <c r="L41" s="3"/>
     </row>
     <row r="42" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="39"/>
-      <c r="B42" s="40"/>
+      <c r="A42" s="42"/>
+      <c r="B42" s="43"/>
       <c r="C42" s="26"/>
       <c r="D42" s="6"/>
       <c r="E42" s="6" t="s">
@@ -2241,40 +2241,40 @@
       <c r="L42" s="7"/>
     </row>
     <row r="43" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="73" t="s">
+      <c r="A43" s="54" t="s">
         <v>94</v>
       </c>
-      <c r="B43" s="74"/>
-      <c r="C43" s="74"/>
-      <c r="D43" s="74"/>
-      <c r="E43" s="74"/>
-      <c r="F43" s="74"/>
-      <c r="G43" s="74"/>
-      <c r="H43" s="74"/>
-      <c r="I43" s="74"/>
-      <c r="J43" s="74"/>
-      <c r="K43" s="74"/>
-      <c r="L43" s="75"/>
+      <c r="B43" s="55"/>
+      <c r="C43" s="55"/>
+      <c r="D43" s="55"/>
+      <c r="E43" s="55"/>
+      <c r="F43" s="55"/>
+      <c r="G43" s="55"/>
+      <c r="H43" s="55"/>
+      <c r="I43" s="55"/>
+      <c r="J43" s="55"/>
+      <c r="K43" s="55"/>
+      <c r="L43" s="56"/>
     </row>
     <row r="44" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="76"/>
-      <c r="B44" s="77"/>
-      <c r="C44" s="77"/>
-      <c r="D44" s="77"/>
-      <c r="E44" s="77"/>
-      <c r="F44" s="77"/>
-      <c r="G44" s="77"/>
-      <c r="H44" s="77"/>
-      <c r="I44" s="77"/>
-      <c r="J44" s="77"/>
-      <c r="K44" s="77"/>
-      <c r="L44" s="78"/>
+      <c r="A44" s="57"/>
+      <c r="B44" s="58"/>
+      <c r="C44" s="58"/>
+      <c r="D44" s="58"/>
+      <c r="E44" s="58"/>
+      <c r="F44" s="58"/>
+      <c r="G44" s="58"/>
+      <c r="H44" s="58"/>
+      <c r="I44" s="58"/>
+      <c r="J44" s="58"/>
+      <c r="K44" s="58"/>
+      <c r="L44" s="59"/>
     </row>
     <row r="45" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="45" t="s">
+      <c r="A45" s="44" t="s">
         <v>95</v>
       </c>
-      <c r="B45" s="46"/>
+      <c r="B45" s="45"/>
       <c r="C45" s="8" t="s">
         <v>17</v>
       </c>
@@ -2302,8 +2302,8 @@
       <c r="L45" s="2"/>
     </row>
     <row r="46" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="47"/>
-      <c r="B46" s="48"/>
+      <c r="A46" s="46"/>
+      <c r="B46" s="47"/>
       <c r="C46" s="32" t="s">
         <v>141</v>
       </c>
@@ -2334,10 +2334,10 @@
       <c r="L46" s="7"/>
     </row>
     <row r="47" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="45" t="s">
+      <c r="A47" s="44" t="s">
         <v>96</v>
       </c>
-      <c r="B47" s="46"/>
+      <c r="B47" s="45"/>
       <c r="C47" s="27" t="s">
         <v>141</v>
       </c>
@@ -2364,8 +2364,8 @@
       <c r="L47" s="2"/>
     </row>
     <row r="48" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="47"/>
-      <c r="B48" s="48"/>
+      <c r="A48" s="46"/>
+      <c r="B48" s="47"/>
       <c r="C48" s="28"/>
       <c r="D48" s="6" t="s">
         <v>25</v>
@@ -2390,10 +2390,10 @@
       <c r="L48" s="7"/>
     </row>
     <row r="49" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="45" t="s">
+      <c r="A49" s="44" t="s">
         <v>100</v>
       </c>
-      <c r="B49" s="46"/>
+      <c r="B49" s="45"/>
       <c r="C49" s="27" t="s">
         <v>141</v>
       </c>
@@ -2420,8 +2420,8 @@
       <c r="L49" s="2"/>
     </row>
     <row r="50" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="47"/>
-      <c r="B50" s="48"/>
+      <c r="A50" s="46"/>
+      <c r="B50" s="47"/>
       <c r="C50" s="28"/>
       <c r="D50" s="6" t="s">
         <v>25</v>
@@ -2446,10 +2446,10 @@
       <c r="L50" s="7"/>
     </row>
     <row r="51" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="37" t="s">
+      <c r="A51" s="38" t="s">
         <v>101</v>
       </c>
-      <c r="B51" s="38"/>
+      <c r="B51" s="39"/>
       <c r="C51" s="25" t="s">
         <v>141</v>
       </c>
@@ -2468,8 +2468,8 @@
       <c r="L51" s="2"/>
     </row>
     <row r="52" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="39"/>
-      <c r="B52" s="40"/>
+      <c r="A52" s="42"/>
+      <c r="B52" s="43"/>
       <c r="C52" s="26"/>
       <c r="D52" s="5"/>
       <c r="E52" s="6" t="s">
@@ -2484,10 +2484,10 @@
       <c r="L52" s="7"/>
     </row>
     <row r="53" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="37" t="s">
+      <c r="A53" s="38" t="s">
         <v>102</v>
       </c>
-      <c r="B53" s="38"/>
+      <c r="B53" s="39"/>
       <c r="C53" s="25" t="s">
         <v>141</v>
       </c>
@@ -2505,8 +2505,8 @@
       <c r="L53" s="2"/>
     </row>
     <row r="54" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="39"/>
-      <c r="B54" s="40"/>
+      <c r="A54" s="42"/>
+      <c r="B54" s="43"/>
       <c r="C54" s="26"/>
       <c r="D54" s="5"/>
       <c r="E54" s="6" t="s">
@@ -2520,10 +2520,10 @@
       <c r="L54" s="7"/>
     </row>
     <row r="55" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="37" t="s">
+      <c r="A55" s="38" t="s">
         <v>103</v>
       </c>
-      <c r="B55" s="38"/>
+      <c r="B55" s="39"/>
       <c r="C55" s="29" t="s">
         <v>141</v>
       </c>
@@ -2542,8 +2542,8 @@
       <c r="L55" s="2"/>
     </row>
     <row r="56" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="39"/>
-      <c r="B56" s="40"/>
+      <c r="A56" s="42"/>
+      <c r="B56" s="43"/>
       <c r="C56" s="30"/>
       <c r="D56" s="5"/>
       <c r="E56" s="6" t="s">
@@ -2557,10 +2557,10 @@
       <c r="L56" s="7"/>
     </row>
     <row r="57" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="41" t="s">
+      <c r="A57" s="48" t="s">
         <v>104</v>
       </c>
-      <c r="B57" s="42"/>
+      <c r="B57" s="49"/>
       <c r="C57" s="22" t="s">
         <v>141</v>
       </c>
@@ -2581,8 +2581,8 @@
       <c r="L57" s="12"/>
     </row>
     <row r="58" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="43"/>
-      <c r="B58" s="44"/>
+      <c r="A58" s="50"/>
+      <c r="B58" s="51"/>
       <c r="C58" s="24"/>
       <c r="D58" s="18"/>
       <c r="E58" s="13" t="s">
@@ -2599,10 +2599,10 @@
       <c r="L58" s="14"/>
     </row>
     <row r="59" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="37" t="s">
+      <c r="A59" s="38" t="s">
         <v>133</v>
       </c>
-      <c r="B59" s="38"/>
+      <c r="B59" s="39"/>
       <c r="C59" s="33" t="s">
         <v>141</v>
       </c>
@@ -2618,8 +2618,8 @@
       <c r="L59" s="3"/>
     </row>
     <row r="60" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="39"/>
-      <c r="B60" s="40"/>
+      <c r="A60" s="42"/>
+      <c r="B60" s="43"/>
       <c r="C60" s="33"/>
       <c r="D60" s="4"/>
       <c r="I60" t="s">
@@ -2628,10 +2628,10 @@
       <c r="L60" s="3"/>
     </row>
     <row r="61" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="41" t="s">
+      <c r="A61" s="48" t="s">
         <v>106</v>
       </c>
-      <c r="B61" s="42"/>
+      <c r="B61" s="49"/>
       <c r="C61" s="22" t="s">
         <v>141</v>
       </c>
@@ -2650,8 +2650,8 @@
       <c r="L61" s="12"/>
     </row>
     <row r="62" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="43"/>
-      <c r="B62" s="44"/>
+      <c r="A62" s="50"/>
+      <c r="B62" s="51"/>
       <c r="C62" s="24"/>
       <c r="D62" s="18"/>
       <c r="E62" s="13"/>
@@ -2664,10 +2664,10 @@
       <c r="L62" s="14"/>
     </row>
     <row r="63" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="41" t="s">
+      <c r="A63" s="48" t="s">
         <v>105</v>
       </c>
-      <c r="B63" s="42"/>
+      <c r="B63" s="49"/>
       <c r="C63" s="22" t="s">
         <v>141</v>
       </c>
@@ -2686,8 +2686,8 @@
       <c r="L63" s="12"/>
     </row>
     <row r="64" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="43"/>
-      <c r="B64" s="44"/>
+      <c r="A64" s="50"/>
+      <c r="B64" s="51"/>
       <c r="C64" s="24"/>
       <c r="D64" s="18"/>
       <c r="E64" s="13"/>
@@ -2700,10 +2700,10 @@
       <c r="L64" s="14"/>
     </row>
     <row r="65" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="41" t="s">
+      <c r="A65" s="48" t="s">
         <v>107</v>
       </c>
-      <c r="B65" s="42"/>
+      <c r="B65" s="49"/>
       <c r="C65" s="22" t="s">
         <v>141</v>
       </c>
@@ -2726,8 +2726,8 @@
       <c r="L65" s="12"/>
     </row>
     <row r="66" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="53"/>
-      <c r="B66" s="54"/>
+      <c r="A66" s="52"/>
+      <c r="B66" s="53"/>
       <c r="C66" s="23"/>
       <c r="D66" s="15"/>
       <c r="E66" s="15" t="s">
@@ -2746,8 +2746,8 @@
       <c r="L66" s="16"/>
     </row>
     <row r="67" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="53"/>
-      <c r="B67" s="54"/>
+      <c r="A67" s="52"/>
+      <c r="B67" s="53"/>
       <c r="C67" s="23"/>
       <c r="D67" s="15"/>
       <c r="E67" s="15" t="s">
@@ -2766,8 +2766,8 @@
       <c r="L67" s="16"/>
     </row>
     <row r="68" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="43"/>
-      <c r="B68" s="44"/>
+      <c r="A68" s="50"/>
+      <c r="B68" s="51"/>
       <c r="C68" s="24"/>
       <c r="D68" s="13"/>
       <c r="E68" s="13" t="s">
@@ -2786,10 +2786,10 @@
       <c r="L68" s="14"/>
     </row>
     <row r="69" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="41" t="s">
+      <c r="A69" s="48" t="s">
         <v>112</v>
       </c>
-      <c r="B69" s="42"/>
+      <c r="B69" s="49"/>
       <c r="C69" s="22" t="s">
         <v>141</v>
       </c>
@@ -2816,8 +2816,8 @@
       <c r="L69" s="12"/>
     </row>
     <row r="70" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="53"/>
-      <c r="B70" s="54"/>
+      <c r="A70" s="52"/>
+      <c r="B70" s="53"/>
       <c r="C70" s="23"/>
       <c r="D70" s="19"/>
       <c r="E70" s="15" t="s">
@@ -2840,8 +2840,8 @@
       <c r="L70" s="16"/>
     </row>
     <row r="71" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="53"/>
-      <c r="B71" s="54"/>
+      <c r="A71" s="52"/>
+      <c r="B71" s="53"/>
       <c r="C71" s="23"/>
       <c r="D71" s="19"/>
       <c r="E71" s="15" t="s">
@@ -2862,8 +2862,8 @@
       <c r="L71" s="16"/>
     </row>
     <row r="72" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="43"/>
-      <c r="B72" s="44"/>
+      <c r="A72" s="50"/>
+      <c r="B72" s="51"/>
       <c r="C72" s="24"/>
       <c r="D72" s="18"/>
       <c r="E72" s="13" t="s">
@@ -2880,10 +2880,10 @@
       <c r="L72" s="14"/>
     </row>
     <row r="73" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="37" t="s">
+      <c r="A73" s="38" t="s">
         <v>125</v>
       </c>
-      <c r="B73" s="38"/>
+      <c r="B73" s="39"/>
       <c r="C73" s="25" t="s">
         <v>141</v>
       </c>
@@ -2911,8 +2911,8 @@
       <c r="L73" s="2"/>
     </row>
     <row r="74" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="71"/>
-      <c r="B74" s="72"/>
+      <c r="A74" s="40"/>
+      <c r="B74" s="41"/>
       <c r="C74" s="33"/>
       <c r="D74" s="4"/>
       <c r="E74" t="s">
@@ -2936,14 +2936,14 @@
       <c r="L74" s="3"/>
     </row>
     <row r="75" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="71"/>
-      <c r="B75" s="72"/>
+      <c r="A75" s="40"/>
+      <c r="B75" s="41"/>
       <c r="C75" s="33"/>
       <c r="D75" s="5"/>
-      <c r="E75" s="80" t="s">
+      <c r="E75" s="37" t="s">
         <v>130</v>
       </c>
-      <c r="F75" s="80"/>
+      <c r="F75" s="37"/>
       <c r="G75" s="6" t="s">
         <v>117</v>
       </c>
@@ -2956,8 +2956,8 @@
       <c r="L75" s="7"/>
     </row>
     <row r="76" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="71"/>
-      <c r="B76" s="72"/>
+      <c r="A76" s="40"/>
+      <c r="B76" s="41"/>
       <c r="C76" s="33" t="s">
         <v>141</v>
       </c>
@@ -2984,8 +2984,8 @@
       <c r="L76" s="2"/>
     </row>
     <row r="77" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="71"/>
-      <c r="B77" s="72"/>
+      <c r="A77" s="40"/>
+      <c r="B77" s="41"/>
       <c r="C77" s="33"/>
       <c r="D77" s="4"/>
       <c r="E77" t="s">
@@ -3006,24 +3006,24 @@
       <c r="L77" s="3"/>
     </row>
     <row r="78" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="71"/>
-      <c r="B78" s="72"/>
+      <c r="A78" s="40"/>
+      <c r="B78" s="41"/>
       <c r="C78" s="33"/>
       <c r="D78" s="5"/>
-      <c r="E78" s="80" t="s">
+      <c r="E78" s="37" t="s">
         <v>131</v>
       </c>
-      <c r="F78" s="80"/>
-      <c r="G78" s="80"/>
-      <c r="H78" s="80"/>
+      <c r="F78" s="37"/>
+      <c r="G78" s="37"/>
+      <c r="H78" s="37"/>
       <c r="I78" s="6"/>
       <c r="J78" s="6"/>
       <c r="K78" s="6"/>
       <c r="L78" s="7"/>
     </row>
     <row r="79" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="71"/>
-      <c r="B79" s="72"/>
+      <c r="A79" s="40"/>
+      <c r="B79" s="41"/>
       <c r="C79" s="33"/>
       <c r="D79" s="8"/>
       <c r="H79" s="1"/>
@@ -3033,15 +3033,15 @@
       <c r="L79" s="2"/>
     </row>
     <row r="80" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="71"/>
-      <c r="B80" s="72"/>
+      <c r="A80" s="40"/>
+      <c r="B80" s="41"/>
       <c r="C80" s="33"/>
       <c r="D80" s="4"/>
       <c r="L80" s="3"/>
     </row>
     <row r="81" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="39"/>
-      <c r="B81" s="40"/>
+      <c r="A81" s="42"/>
+      <c r="B81" s="43"/>
       <c r="C81" s="26"/>
       <c r="D81" s="5"/>
       <c r="E81" s="6"/>
@@ -3055,6 +3055,26 @@
     </row>
   </sheetData>
   <mergeCells count="35">
+    <mergeCell ref="A4:B5"/>
+    <mergeCell ref="A6:B7"/>
+    <mergeCell ref="A8:B11"/>
+    <mergeCell ref="A2:L3"/>
+    <mergeCell ref="A22:B23"/>
+    <mergeCell ref="A12:B13"/>
+    <mergeCell ref="A14:B15"/>
+    <mergeCell ref="A16:B17"/>
+    <mergeCell ref="A18:B19"/>
+    <mergeCell ref="A20:B21"/>
+    <mergeCell ref="A40:B42"/>
+    <mergeCell ref="A45:B46"/>
+    <mergeCell ref="A43:L44"/>
+    <mergeCell ref="O6:P6"/>
+    <mergeCell ref="O8:P8"/>
+    <mergeCell ref="A24:B25"/>
+    <mergeCell ref="A26:L27"/>
+    <mergeCell ref="A28:B31"/>
+    <mergeCell ref="A32:L33"/>
+    <mergeCell ref="A34:B39"/>
     <mergeCell ref="G78:H78"/>
     <mergeCell ref="A73:B81"/>
     <mergeCell ref="A47:B48"/>
@@ -3065,26 +3085,6 @@
     <mergeCell ref="A63:B64"/>
     <mergeCell ref="A65:B68"/>
     <mergeCell ref="A69:B72"/>
-    <mergeCell ref="A40:B42"/>
-    <mergeCell ref="A45:B46"/>
-    <mergeCell ref="A43:L44"/>
-    <mergeCell ref="O6:P6"/>
-    <mergeCell ref="O8:P8"/>
-    <mergeCell ref="A24:B25"/>
-    <mergeCell ref="A26:L27"/>
-    <mergeCell ref="A28:B31"/>
-    <mergeCell ref="A32:L33"/>
-    <mergeCell ref="A34:B39"/>
-    <mergeCell ref="A4:B5"/>
-    <mergeCell ref="A6:B7"/>
-    <mergeCell ref="A8:B11"/>
-    <mergeCell ref="A2:L3"/>
-    <mergeCell ref="A22:B23"/>
-    <mergeCell ref="A12:B13"/>
-    <mergeCell ref="A14:B15"/>
-    <mergeCell ref="A16:B17"/>
-    <mergeCell ref="A18:B19"/>
-    <mergeCell ref="A20:B21"/>
     <mergeCell ref="A51:B52"/>
     <mergeCell ref="A53:B54"/>
     <mergeCell ref="A55:B56"/>
